--- a/public/assets/templates/operasional/pemantauan_pompa_utility.xlsx
+++ b/public/assets/templates/operasional/pemantauan_pompa_utility.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\pt_bas\Engineering\public\assets\templates\operasional\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E18AC546-0FAD-492A-A919-6C0775F1630D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A9E10F-C01B-4783-809A-CF3F77274E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{85BD6135-9ABD-46C4-8791-20A36F901454}"/>
   </bookViews>
@@ -146,7 +146,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -204,42 +204,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="26"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="26"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="20"/>
       <color theme="1"/>
@@ -248,8 +212,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="22"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -257,7 +220,15 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -520,7 +491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -579,7 +550,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -621,37 +592,22 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -681,8 +637,8 @@
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1610360</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>174708</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>25566</xdr:rowOff>
     </xdr:to>
@@ -1025,17 +981,7 @@
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10.81640625" customWidth="1"/>
-    <col min="2" max="2" width="44.26953125" customWidth="1"/>
-    <col min="3" max="5" width="48.81640625" customWidth="1"/>
-    <col min="6" max="6" width="48.54296875" customWidth="1"/>
-    <col min="7" max="7" width="44.26953125" customWidth="1"/>
-    <col min="8" max="8" width="48.81640625" customWidth="1"/>
-    <col min="9" max="9" width="44.26953125" customWidth="1"/>
-    <col min="10" max="10" width="48.81640625" customWidth="1"/>
-    <col min="11" max="20" width="22.1796875" customWidth="1"/>
-    <col min="21" max="21" width="38" customWidth="1"/>
-    <col min="22" max="22" width="33.7265625" customWidth="1"/>
-    <col min="23" max="23" width="33.453125" customWidth="1"/>
+    <col min="2" max="23" width="20.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" thickTop="1">
@@ -1317,1037 +1263,1037 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="28.5">
+    <row r="8" spans="1:23" ht="15.5">
       <c r="A8" s="5">
         <v>1</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="42"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="42"/>
-      <c r="Q8" s="42"/>
-      <c r="R8" s="42"/>
-      <c r="S8" s="42"/>
-      <c r="T8" s="42"/>
-      <c r="U8" s="42"/>
-      <c r="V8" s="42"/>
-      <c r="W8" s="42"/>
-    </row>
-    <row r="9" spans="1:23" ht="28.5">
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="35"/>
+    </row>
+    <row r="9" spans="1:23" ht="15.5">
       <c r="A9" s="5">
         <v>2</v>
       </c>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="42"/>
-      <c r="P9" s="42"/>
-      <c r="Q9" s="42"/>
-      <c r="R9" s="42"/>
-      <c r="S9" s="42"/>
-      <c r="T9" s="42"/>
-      <c r="U9" s="42"/>
-      <c r="V9" s="42"/>
-      <c r="W9" s="42"/>
-    </row>
-    <row r="10" spans="1:23" ht="28.5">
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35"/>
+      <c r="S9" s="35"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="35"/>
+      <c r="W9" s="35"/>
+    </row>
+    <row r="10" spans="1:23" ht="15.5">
       <c r="A10" s="5">
         <v>3</v>
       </c>
-      <c r="B10" s="41"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="42"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="42"/>
-      <c r="S10" s="42"/>
-      <c r="T10" s="42"/>
-      <c r="U10" s="42"/>
-      <c r="V10" s="42"/>
-      <c r="W10" s="42"/>
-    </row>
-    <row r="11" spans="1:23" ht="28.5">
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="35"/>
+    </row>
+    <row r="11" spans="1:23" ht="15.5">
       <c r="A11" s="5">
         <v>4</v>
       </c>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="42"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="42"/>
-      <c r="P11" s="42"/>
-      <c r="Q11" s="42"/>
-      <c r="R11" s="42"/>
-      <c r="S11" s="42"/>
-      <c r="T11" s="42"/>
-      <c r="U11" s="42"/>
-      <c r="V11" s="42"/>
-      <c r="W11" s="42"/>
-    </row>
-    <row r="12" spans="1:23" ht="28.5">
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="35"/>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="35"/>
+      <c r="W11" s="35"/>
+    </row>
+    <row r="12" spans="1:23" ht="15.5">
       <c r="A12" s="5">
         <v>5</v>
       </c>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="42"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="42"/>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
-      <c r="T12" s="42"/>
-      <c r="U12" s="42"/>
-      <c r="V12" s="42"/>
-      <c r="W12" s="42"/>
-    </row>
-    <row r="13" spans="1:23" ht="28.5">
+      <c r="B12" s="35"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="35"/>
+      <c r="F12" s="35"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="35"/>
+      <c r="T12" s="35"/>
+      <c r="U12" s="35"/>
+      <c r="V12" s="35"/>
+      <c r="W12" s="35"/>
+    </row>
+    <row r="13" spans="1:23" ht="15.5">
       <c r="A13" s="5">
         <v>6</v>
       </c>
-      <c r="B13" s="41"/>
-      <c r="C13" s="41"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="42"/>
-      <c r="M13" s="42"/>
-      <c r="N13" s="42"/>
-      <c r="O13" s="42"/>
-      <c r="P13" s="42"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="42"/>
-      <c r="U13" s="42"/>
-      <c r="V13" s="42"/>
-      <c r="W13" s="42"/>
-    </row>
-    <row r="14" spans="1:23" ht="28.5">
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="35"/>
+      <c r="V13" s="35"/>
+      <c r="W13" s="35"/>
+    </row>
+    <row r="14" spans="1:23" ht="15.5">
       <c r="A14" s="5">
         <v>7</v>
       </c>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="42"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="42"/>
-      <c r="O14" s="42"/>
-      <c r="P14" s="42"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="42"/>
-      <c r="U14" s="42"/>
-      <c r="V14" s="42"/>
-      <c r="W14" s="42"/>
-    </row>
-    <row r="15" spans="1:23" ht="28.5">
+      <c r="B14" s="35"/>
+      <c r="C14" s="35"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="35"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="35"/>
+      <c r="V14" s="35"/>
+      <c r="W14" s="35"/>
+    </row>
+    <row r="15" spans="1:23" ht="15.5">
       <c r="A15" s="5">
         <v>8</v>
       </c>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="42"/>
-      <c r="M15" s="42"/>
-      <c r="N15" s="42"/>
-      <c r="O15" s="42"/>
-      <c r="P15" s="42"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="42"/>
-      <c r="U15" s="42"/>
-      <c r="V15" s="42"/>
-      <c r="W15" s="42"/>
-    </row>
-    <row r="16" spans="1:23" ht="28.5">
+      <c r="B15" s="35"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="35"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="35"/>
+      <c r="W15" s="35"/>
+    </row>
+    <row r="16" spans="1:23" ht="15.5">
       <c r="A16" s="5">
         <v>9</v>
       </c>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="42"/>
-      <c r="L16" s="42"/>
-      <c r="M16" s="42"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="42"/>
-      <c r="P16" s="42"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="42"/>
-      <c r="U16" s="42"/>
-      <c r="V16" s="42"/>
-      <c r="W16" s="42"/>
-    </row>
-    <row r="17" spans="1:23" ht="28.5">
+      <c r="B16" s="35"/>
+      <c r="C16" s="35"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="35"/>
+    </row>
+    <row r="17" spans="1:23" ht="15.5">
       <c r="A17" s="5">
         <v>10</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="42"/>
-      <c r="M17" s="42"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="42"/>
-      <c r="P17" s="42"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="42"/>
-      <c r="U17" s="42"/>
-      <c r="V17" s="42"/>
-      <c r="W17" s="42"/>
-    </row>
-    <row r="18" spans="1:23" ht="28.5">
+      <c r="B17" s="35"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="35"/>
+      <c r="U17" s="35"/>
+      <c r="V17" s="35"/>
+      <c r="W17" s="35"/>
+    </row>
+    <row r="18" spans="1:23" ht="15.5">
       <c r="A18" s="5">
         <v>11</v>
       </c>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42"/>
-      <c r="J18" s="42"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="42"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="42"/>
-      <c r="P18" s="42"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="42"/>
-      <c r="T18" s="42"/>
-      <c r="U18" s="42"/>
-      <c r="V18" s="42"/>
-      <c r="W18" s="42"/>
-    </row>
-    <row r="19" spans="1:23" ht="28.5">
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="35"/>
+      <c r="V18" s="35"/>
+      <c r="W18" s="35"/>
+    </row>
+    <row r="19" spans="1:23" ht="15.5">
       <c r="A19" s="5">
         <v>12</v>
       </c>
-      <c r="B19" s="41"/>
-      <c r="C19" s="41"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42"/>
-      <c r="J19" s="42"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="42"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="42"/>
-      <c r="P19" s="42"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="42"/>
-      <c r="U19" s="42"/>
-      <c r="V19" s="42"/>
-      <c r="W19" s="42"/>
-    </row>
-    <row r="20" spans="1:23" ht="28.5">
+      <c r="B19" s="35"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="35"/>
+      <c r="V19" s="35"/>
+      <c r="W19" s="35"/>
+    </row>
+    <row r="20" spans="1:23" ht="15.5">
       <c r="A20" s="5">
         <v>13</v>
       </c>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="42"/>
-      <c r="P20" s="42"/>
-      <c r="Q20" s="42"/>
-      <c r="R20" s="42"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="42"/>
-      <c r="U20" s="42"/>
-      <c r="V20" s="42"/>
-      <c r="W20" s="42"/>
-    </row>
-    <row r="21" spans="1:23" ht="28.5">
+      <c r="B20" s="35"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="35"/>
+      <c r="V20" s="35"/>
+      <c r="W20" s="35"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.5">
       <c r="A21" s="5">
         <v>14</v>
       </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="41"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="42"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="42"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="42"/>
-      <c r="P21" s="42"/>
-      <c r="Q21" s="42"/>
-      <c r="R21" s="42"/>
-      <c r="S21" s="42"/>
-      <c r="T21" s="42"/>
-      <c r="U21" s="42"/>
-      <c r="V21" s="42"/>
-      <c r="W21" s="42"/>
-    </row>
-    <row r="22" spans="1:23" ht="28.5">
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="35"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="35"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="35"/>
+      <c r="V21" s="35"/>
+      <c r="W21" s="35"/>
+    </row>
+    <row r="22" spans="1:23" ht="15.5">
       <c r="A22" s="5">
         <v>15</v>
       </c>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
-      <c r="J22" s="42"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="42"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="42"/>
-      <c r="O22" s="42"/>
-      <c r="P22" s="42"/>
-      <c r="Q22" s="42"/>
-      <c r="R22" s="42"/>
-      <c r="S22" s="42"/>
-      <c r="T22" s="42"/>
-      <c r="U22" s="42"/>
-      <c r="V22" s="42"/>
-      <c r="W22" s="42"/>
-    </row>
-    <row r="23" spans="1:23" ht="28.5">
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="35"/>
+      <c r="V22" s="35"/>
+      <c r="W22" s="35"/>
+    </row>
+    <row r="23" spans="1:23" ht="15.5">
       <c r="A23" s="5">
         <v>16</v>
       </c>
-      <c r="B23" s="41"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42"/>
-      <c r="J23" s="42"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="42"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="42"/>
-      <c r="O23" s="42"/>
-      <c r="P23" s="42"/>
-      <c r="Q23" s="42"/>
-      <c r="R23" s="42"/>
-      <c r="S23" s="42"/>
-      <c r="T23" s="42"/>
-      <c r="U23" s="42"/>
-      <c r="V23" s="42"/>
-      <c r="W23" s="42"/>
-    </row>
-    <row r="24" spans="1:23" ht="28.5">
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="35"/>
+    </row>
+    <row r="24" spans="1:23" ht="15.5">
       <c r="A24" s="5">
         <v>17</v>
       </c>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
-      <c r="G24" s="42"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="42"/>
-      <c r="J24" s="42"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="42"/>
-      <c r="M24" s="42"/>
-      <c r="N24" s="42"/>
-      <c r="O24" s="42"/>
-      <c r="P24" s="42"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="42"/>
-      <c r="S24" s="42"/>
-      <c r="T24" s="42"/>
-      <c r="U24" s="42"/>
-      <c r="V24" s="42"/>
-      <c r="W24" s="42"/>
-    </row>
-    <row r="25" spans="1:23" ht="28.5">
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="35"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="35"/>
+      <c r="W24" s="35"/>
+    </row>
+    <row r="25" spans="1:23" ht="15.5">
       <c r="A25" s="5">
         <v>18</v>
       </c>
-      <c r="B25" s="41"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
-      <c r="G25" s="42"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="42"/>
-      <c r="J25" s="42"/>
-      <c r="K25" s="42"/>
-      <c r="L25" s="42"/>
-      <c r="M25" s="42"/>
-      <c r="N25" s="42"/>
-      <c r="O25" s="42"/>
-      <c r="P25" s="42"/>
-      <c r="Q25" s="42"/>
-      <c r="R25" s="42"/>
-      <c r="S25" s="42"/>
-      <c r="T25" s="42"/>
-      <c r="U25" s="42"/>
-      <c r="V25" s="42"/>
-      <c r="W25" s="42"/>
-    </row>
-    <row r="26" spans="1:23" ht="28.5">
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35"/>
+      <c r="R25" s="35"/>
+      <c r="S25" s="35"/>
+      <c r="T25" s="35"/>
+      <c r="U25" s="35"/>
+      <c r="V25" s="35"/>
+      <c r="W25" s="35"/>
+    </row>
+    <row r="26" spans="1:23" ht="15.5">
       <c r="A26" s="5">
         <v>19</v>
       </c>
-      <c r="B26" s="41"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
-      <c r="G26" s="42"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42"/>
-      <c r="J26" s="42"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="42"/>
-      <c r="M26" s="42"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="42"/>
-      <c r="P26" s="42"/>
-      <c r="Q26" s="42"/>
-      <c r="R26" s="42"/>
-      <c r="S26" s="42"/>
-      <c r="T26" s="42"/>
-      <c r="U26" s="42"/>
-      <c r="V26" s="42"/>
-      <c r="W26" s="42"/>
-    </row>
-    <row r="27" spans="1:23" ht="28.5">
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="35"/>
+      <c r="T26" s="35"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="35"/>
+      <c r="W26" s="35"/>
+    </row>
+    <row r="27" spans="1:23" ht="15.5">
       <c r="A27" s="5">
         <v>20</v>
       </c>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="42"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42"/>
-      <c r="J27" s="42"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="42"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="42"/>
-      <c r="P27" s="42"/>
-      <c r="Q27" s="42"/>
-      <c r="R27" s="42"/>
-      <c r="S27" s="42"/>
-      <c r="T27" s="42"/>
-      <c r="U27" s="42"/>
-      <c r="V27" s="42"/>
-      <c r="W27" s="42"/>
-    </row>
-    <row r="28" spans="1:23" ht="28.5">
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="35"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="35"/>
+      <c r="Q27" s="35"/>
+      <c r="R27" s="35"/>
+      <c r="S27" s="35"/>
+      <c r="T27" s="35"/>
+      <c r="U27" s="35"/>
+      <c r="V27" s="35"/>
+      <c r="W27" s="35"/>
+    </row>
+    <row r="28" spans="1:23" ht="15.5">
       <c r="A28" s="5">
         <v>21</v>
       </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="41"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="42"/>
-      <c r="K28" s="42"/>
-      <c r="L28" s="42"/>
-      <c r="M28" s="42"/>
-      <c r="N28" s="42"/>
-      <c r="O28" s="42"/>
-      <c r="P28" s="42"/>
-      <c r="Q28" s="42"/>
-      <c r="R28" s="42"/>
-      <c r="S28" s="42"/>
-      <c r="T28" s="42"/>
-      <c r="U28" s="42"/>
-      <c r="V28" s="42"/>
-      <c r="W28" s="42"/>
-    </row>
-    <row r="29" spans="1:23" ht="28.5">
+      <c r="B28" s="35"/>
+      <c r="C28" s="35"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="35"/>
+      <c r="R28" s="35"/>
+      <c r="S28" s="35"/>
+      <c r="T28" s="35"/>
+      <c r="U28" s="35"/>
+      <c r="V28" s="35"/>
+      <c r="W28" s="35"/>
+    </row>
+    <row r="29" spans="1:23" ht="15.5">
       <c r="A29" s="5">
         <v>22</v>
       </c>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="42"/>
-      <c r="E29" s="42"/>
-      <c r="F29" s="42"/>
-      <c r="G29" s="42"/>
-      <c r="H29" s="42"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="42"/>
-      <c r="L29" s="42"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="42"/>
-      <c r="O29" s="42"/>
-      <c r="P29" s="42"/>
-      <c r="Q29" s="42"/>
-      <c r="R29" s="42"/>
-      <c r="S29" s="42"/>
-      <c r="T29" s="42"/>
-      <c r="U29" s="42"/>
-      <c r="V29" s="42"/>
-      <c r="W29" s="42"/>
-    </row>
-    <row r="30" spans="1:23" ht="28.5">
+      <c r="B29" s="35"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
+      <c r="O29" s="35"/>
+      <c r="P29" s="35"/>
+      <c r="Q29" s="35"/>
+      <c r="R29" s="35"/>
+      <c r="S29" s="35"/>
+      <c r="T29" s="35"/>
+      <c r="U29" s="35"/>
+      <c r="V29" s="35"/>
+      <c r="W29" s="35"/>
+    </row>
+    <row r="30" spans="1:23" ht="15.5">
       <c r="A30" s="5">
         <v>23</v>
       </c>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="42"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="42"/>
-      <c r="K30" s="42"/>
-      <c r="L30" s="42"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="42"/>
-      <c r="S30" s="42"/>
-      <c r="T30" s="42"/>
-      <c r="U30" s="42"/>
-      <c r="V30" s="42"/>
-      <c r="W30" s="42"/>
-    </row>
-    <row r="31" spans="1:23" ht="28.5">
+      <c r="B30" s="35"/>
+      <c r="C30" s="35"/>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="35"/>
+      <c r="R30" s="35"/>
+      <c r="S30" s="35"/>
+      <c r="T30" s="35"/>
+      <c r="U30" s="35"/>
+      <c r="V30" s="35"/>
+      <c r="W30" s="35"/>
+    </row>
+    <row r="31" spans="1:23" ht="15.5">
       <c r="A31" s="5">
         <v>24</v>
       </c>
-      <c r="B31" s="41"/>
-      <c r="C31" s="41"/>
-      <c r="D31" s="42"/>
-      <c r="E31" s="42"/>
-      <c r="F31" s="42"/>
-      <c r="G31" s="42"/>
-      <c r="H31" s="42"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="42"/>
-      <c r="K31" s="42"/>
-      <c r="L31" s="42"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="42"/>
-      <c r="O31" s="42"/>
-      <c r="P31" s="42"/>
-      <c r="Q31" s="42"/>
-      <c r="R31" s="42"/>
-      <c r="S31" s="42"/>
-      <c r="T31" s="42"/>
-      <c r="U31" s="42"/>
-      <c r="V31" s="42"/>
-      <c r="W31" s="42"/>
-    </row>
-    <row r="32" spans="1:23" ht="28.5">
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="35"/>
+      <c r="V31" s="35"/>
+      <c r="W31" s="35"/>
+    </row>
+    <row r="32" spans="1:23" ht="15.5">
       <c r="A32" s="5">
         <v>25</v>
       </c>
-      <c r="B32" s="41"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="42"/>
-      <c r="K32" s="42"/>
-      <c r="L32" s="42"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="42"/>
-      <c r="S32" s="42"/>
-      <c r="T32" s="42"/>
-      <c r="U32" s="42"/>
-      <c r="V32" s="42"/>
-      <c r="W32" s="42"/>
-    </row>
-    <row r="33" spans="1:23" ht="28.5">
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
+      <c r="R32" s="35"/>
+      <c r="S32" s="35"/>
+      <c r="T32" s="35"/>
+      <c r="U32" s="35"/>
+      <c r="V32" s="35"/>
+      <c r="W32" s="35"/>
+    </row>
+    <row r="33" spans="1:23" ht="15.5">
       <c r="A33" s="5">
         <v>26</v>
       </c>
-      <c r="B33" s="41"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="42"/>
-      <c r="K33" s="42"/>
-      <c r="L33" s="42"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="42"/>
-      <c r="O33" s="42"/>
-      <c r="P33" s="42"/>
-      <c r="Q33" s="42"/>
-      <c r="R33" s="42"/>
-      <c r="S33" s="42"/>
-      <c r="T33" s="42"/>
-      <c r="U33" s="42"/>
-      <c r="V33" s="42"/>
-      <c r="W33" s="42"/>
-    </row>
-    <row r="34" spans="1:23" ht="28.5">
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="35"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="35"/>
+      <c r="Q33" s="35"/>
+      <c r="R33" s="35"/>
+      <c r="S33" s="35"/>
+      <c r="T33" s="35"/>
+      <c r="U33" s="35"/>
+      <c r="V33" s="35"/>
+      <c r="W33" s="35"/>
+    </row>
+    <row r="34" spans="1:23" ht="15.5">
       <c r="A34" s="5">
         <v>27</v>
       </c>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="42"/>
-      <c r="K34" s="42"/>
-      <c r="L34" s="42"/>
-      <c r="M34" s="42"/>
-      <c r="N34" s="42"/>
-      <c r="O34" s="42"/>
-      <c r="P34" s="42"/>
-      <c r="Q34" s="42"/>
-      <c r="R34" s="42"/>
-      <c r="S34" s="42"/>
-      <c r="T34" s="42"/>
-      <c r="U34" s="42"/>
-      <c r="V34" s="42"/>
-      <c r="W34" s="42"/>
-    </row>
-    <row r="35" spans="1:23" ht="28.5">
+      <c r="B34" s="35"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="35"/>
+      <c r="R34" s="35"/>
+      <c r="S34" s="35"/>
+      <c r="T34" s="35"/>
+      <c r="U34" s="35"/>
+      <c r="V34" s="35"/>
+      <c r="W34" s="35"/>
+    </row>
+    <row r="35" spans="1:23" ht="15.5">
       <c r="A35" s="5">
         <v>28</v>
       </c>
-      <c r="B35" s="41"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="42"/>
-      <c r="H35" s="42"/>
-      <c r="I35" s="42"/>
-      <c r="J35" s="42"/>
-      <c r="K35" s="42"/>
-      <c r="L35" s="42"/>
-      <c r="M35" s="42"/>
-      <c r="N35" s="42"/>
-      <c r="O35" s="42"/>
-      <c r="P35" s="42"/>
-      <c r="Q35" s="42"/>
-      <c r="R35" s="42"/>
-      <c r="S35" s="42"/>
-      <c r="T35" s="42"/>
-      <c r="U35" s="42"/>
-      <c r="V35" s="42"/>
-      <c r="W35" s="42"/>
-    </row>
-    <row r="36" spans="1:23" ht="28.5">
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="35"/>
+      <c r="Q35" s="35"/>
+      <c r="R35" s="35"/>
+      <c r="S35" s="35"/>
+      <c r="T35" s="35"/>
+      <c r="U35" s="35"/>
+      <c r="V35" s="35"/>
+      <c r="W35" s="35"/>
+    </row>
+    <row r="36" spans="1:23" ht="15.5">
       <c r="A36" s="5">
         <v>29</v>
       </c>
-      <c r="B36" s="41"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="42"/>
-      <c r="R36" s="42"/>
-      <c r="S36" s="42"/>
-      <c r="T36" s="42"/>
-      <c r="U36" s="42"/>
-      <c r="V36" s="42"/>
-      <c r="W36" s="42"/>
-    </row>
-    <row r="37" spans="1:23" ht="28.5">
+      <c r="B36" s="35"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="35"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="35"/>
+      <c r="Q36" s="35"/>
+      <c r="R36" s="35"/>
+      <c r="S36" s="35"/>
+      <c r="T36" s="35"/>
+      <c r="U36" s="35"/>
+      <c r="V36" s="35"/>
+      <c r="W36" s="35"/>
+    </row>
+    <row r="37" spans="1:23" ht="15.5">
       <c r="A37" s="5">
         <v>30</v>
       </c>
-      <c r="B37" s="41"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="42"/>
-      <c r="E37" s="42"/>
-      <c r="F37" s="42"/>
-      <c r="G37" s="42"/>
-      <c r="H37" s="42"/>
-      <c r="I37" s="42"/>
-      <c r="J37" s="42"/>
-      <c r="K37" s="42"/>
-      <c r="L37" s="42"/>
-      <c r="M37" s="42"/>
-      <c r="N37" s="42"/>
-      <c r="O37" s="42"/>
-      <c r="P37" s="42"/>
-      <c r="Q37" s="42"/>
-      <c r="R37" s="42"/>
-      <c r="S37" s="42"/>
-      <c r="T37" s="42"/>
-      <c r="U37" s="42"/>
-      <c r="V37" s="42"/>
-      <c r="W37" s="42"/>
-    </row>
-    <row r="38" spans="1:23" ht="28.5">
+      <c r="B37" s="35"/>
+      <c r="C37" s="35"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="35"/>
+      <c r="L37" s="35"/>
+      <c r="M37" s="35"/>
+      <c r="N37" s="35"/>
+      <c r="O37" s="35"/>
+      <c r="P37" s="35"/>
+      <c r="Q37" s="35"/>
+      <c r="R37" s="35"/>
+      <c r="S37" s="35"/>
+      <c r="T37" s="35"/>
+      <c r="U37" s="35"/>
+      <c r="V37" s="35"/>
+      <c r="W37" s="35"/>
+    </row>
+    <row r="38" spans="1:23" ht="15.5">
       <c r="A38" s="9">
         <v>31</v>
       </c>
-      <c r="B38" s="43"/>
-      <c r="C38" s="43"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="44"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="44"/>
-      <c r="H38" s="44"/>
-      <c r="I38" s="44"/>
-      <c r="J38" s="44"/>
-      <c r="K38" s="44"/>
-      <c r="L38" s="44"/>
-      <c r="M38" s="44"/>
-      <c r="N38" s="44"/>
-      <c r="O38" s="44"/>
-      <c r="P38" s="44"/>
-      <c r="Q38" s="44"/>
-      <c r="R38" s="44"/>
-      <c r="S38" s="44"/>
-      <c r="T38" s="44"/>
-      <c r="U38" s="44"/>
-      <c r="V38" s="44"/>
-      <c r="W38" s="44"/>
-    </row>
-    <row r="39" spans="1:23" ht="33.5">
-      <c r="A39" s="34" t="s">
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36"/>
+      <c r="G38" s="36"/>
+      <c r="H38" s="36"/>
+      <c r="I38" s="36"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="36"/>
+      <c r="L38" s="36"/>
+      <c r="M38" s="36"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="36"/>
+      <c r="P38" s="36"/>
+      <c r="Q38" s="36"/>
+      <c r="R38" s="36"/>
+      <c r="S38" s="36"/>
+      <c r="T38" s="36"/>
+      <c r="U38" s="36"/>
+      <c r="V38" s="36"/>
+      <c r="W38" s="36"/>
+    </row>
+    <row r="39" spans="1:23" ht="15.5">
+      <c r="A39" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="38" t="s">
+      <c r="B39" s="37"/>
+      <c r="C39" s="37"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="37"/>
+      <c r="F39" s="37"/>
+      <c r="G39" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38"/>
-      <c r="J39" s="38"/>
-      <c r="K39" s="38"/>
-      <c r="L39" s="38"/>
-      <c r="M39" s="38"/>
-      <c r="N39" s="38"/>
-      <c r="O39" s="38" t="s">
+      <c r="H39" s="37"/>
+      <c r="I39" s="37"/>
+      <c r="J39" s="37"/>
+      <c r="K39" s="37"/>
+      <c r="L39" s="37"/>
+      <c r="M39" s="37"/>
+      <c r="N39" s="37"/>
+      <c r="O39" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="P39" s="38"/>
-      <c r="Q39" s="38"/>
-      <c r="R39" s="38"/>
-      <c r="S39" s="38"/>
-      <c r="T39" s="38"/>
-      <c r="U39" s="38"/>
-      <c r="V39" s="38"/>
-      <c r="W39" s="38"/>
-    </row>
-    <row r="40" spans="1:23" ht="33.5" customHeight="1">
-      <c r="A40" s="34"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
-      <c r="G40" s="34"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="34"/>
-      <c r="L40" s="34"/>
-      <c r="M40" s="34"/>
-      <c r="N40" s="34"/>
-      <c r="O40" s="40"/>
-      <c r="P40" s="40"/>
-      <c r="Q40" s="40"/>
-      <c r="R40" s="40"/>
-      <c r="S40" s="40"/>
-      <c r="T40" s="40"/>
-      <c r="U40" s="40"/>
-      <c r="V40" s="40"/>
-      <c r="W40" s="40"/>
-    </row>
-    <row r="41" spans="1:23" ht="33.5" customHeight="1">
-      <c r="A41" s="34"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34"/>
-      <c r="I41" s="34"/>
-      <c r="J41" s="34"/>
-      <c r="K41" s="34"/>
-      <c r="L41" s="34"/>
-      <c r="M41" s="34"/>
-      <c r="N41" s="34"/>
-      <c r="O41" s="40"/>
-      <c r="P41" s="40"/>
-      <c r="Q41" s="40"/>
-      <c r="R41" s="40"/>
-      <c r="S41" s="40"/>
-      <c r="T41" s="40"/>
-      <c r="U41" s="40"/>
-      <c r="V41" s="40"/>
-      <c r="W41" s="40"/>
-    </row>
-    <row r="42" spans="1:23" ht="33.5" customHeight="1">
-      <c r="A42" s="34"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="34"/>
-      <c r="M42" s="34"/>
-      <c r="N42" s="34"/>
-      <c r="O42" s="40"/>
-      <c r="P42" s="40"/>
-      <c r="Q42" s="40"/>
-      <c r="R42" s="40"/>
-      <c r="S42" s="40"/>
-      <c r="T42" s="40"/>
-      <c r="U42" s="40"/>
-      <c r="V42" s="40"/>
-      <c r="W42" s="40"/>
-    </row>
-    <row r="43" spans="1:23" ht="33.5" customHeight="1">
-      <c r="A43" s="34"/>
-      <c r="B43" s="34"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-      <c r="J43" s="34"/>
-      <c r="K43" s="34"/>
-      <c r="L43" s="34"/>
-      <c r="M43" s="34"/>
-      <c r="N43" s="34"/>
-      <c r="O43" s="40"/>
-      <c r="P43" s="40"/>
-      <c r="Q43" s="40"/>
-      <c r="R43" s="40"/>
-      <c r="S43" s="40"/>
-      <c r="T43" s="40"/>
-      <c r="U43" s="40"/>
-      <c r="V43" s="40"/>
-      <c r="W43" s="40"/>
-    </row>
-    <row r="44" spans="1:23" ht="33.5" customHeight="1">
-      <c r="A44" s="34"/>
-      <c r="B44" s="34"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="34"/>
-      <c r="F44" s="34"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="34"/>
-      <c r="I44" s="34"/>
-      <c r="J44" s="34"/>
-      <c r="K44" s="34"/>
-      <c r="L44" s="34"/>
-      <c r="M44" s="34"/>
-      <c r="N44" s="34"/>
-      <c r="O44" s="40"/>
-      <c r="P44" s="40"/>
-      <c r="Q44" s="40"/>
-      <c r="R44" s="40"/>
-      <c r="S44" s="40"/>
-      <c r="T44" s="40"/>
-      <c r="U44" s="40"/>
-      <c r="V44" s="40"/>
-      <c r="W44" s="40"/>
-    </row>
-    <row r="45" spans="1:23" ht="31">
-      <c r="A45" s="35" t="s">
+      <c r="P39" s="37"/>
+      <c r="Q39" s="37"/>
+      <c r="R39" s="37"/>
+      <c r="S39" s="37"/>
+      <c r="T39" s="37"/>
+      <c r="U39" s="37"/>
+      <c r="V39" s="37"/>
+      <c r="W39" s="37"/>
+    </row>
+    <row r="40" spans="1:23">
+      <c r="A40" s="37"/>
+      <c r="B40" s="37"/>
+      <c r="C40" s="37"/>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="37"/>
+      <c r="H40" s="37"/>
+      <c r="I40" s="37"/>
+      <c r="J40" s="37"/>
+      <c r="K40" s="37"/>
+      <c r="L40" s="37"/>
+      <c r="M40" s="37"/>
+      <c r="N40" s="37"/>
+      <c r="O40" s="38"/>
+      <c r="P40" s="38"/>
+      <c r="Q40" s="38"/>
+      <c r="R40" s="38"/>
+      <c r="S40" s="38"/>
+      <c r="T40" s="38"/>
+      <c r="U40" s="38"/>
+      <c r="V40" s="38"/>
+      <c r="W40" s="38"/>
+    </row>
+    <row r="41" spans="1:23">
+      <c r="A41" s="37"/>
+      <c r="B41" s="37"/>
+      <c r="C41" s="37"/>
+      <c r="D41" s="37"/>
+      <c r="E41" s="37"/>
+      <c r="F41" s="37"/>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="37"/>
+      <c r="J41" s="37"/>
+      <c r="K41" s="37"/>
+      <c r="L41" s="37"/>
+      <c r="M41" s="37"/>
+      <c r="N41" s="37"/>
+      <c r="O41" s="38"/>
+      <c r="P41" s="38"/>
+      <c r="Q41" s="38"/>
+      <c r="R41" s="38"/>
+      <c r="S41" s="38"/>
+      <c r="T41" s="38"/>
+      <c r="U41" s="38"/>
+      <c r="V41" s="38"/>
+      <c r="W41" s="38"/>
+    </row>
+    <row r="42" spans="1:23">
+      <c r="A42" s="37"/>
+      <c r="B42" s="37"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="37"/>
+      <c r="I42" s="37"/>
+      <c r="J42" s="37"/>
+      <c r="K42" s="37"/>
+      <c r="L42" s="37"/>
+      <c r="M42" s="37"/>
+      <c r="N42" s="37"/>
+      <c r="O42" s="38"/>
+      <c r="P42" s="38"/>
+      <c r="Q42" s="38"/>
+      <c r="R42" s="38"/>
+      <c r="S42" s="38"/>
+      <c r="T42" s="38"/>
+      <c r="U42" s="38"/>
+      <c r="V42" s="38"/>
+      <c r="W42" s="38"/>
+    </row>
+    <row r="43" spans="1:23">
+      <c r="A43" s="37"/>
+      <c r="B43" s="37"/>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="37"/>
+      <c r="H43" s="37"/>
+      <c r="I43" s="37"/>
+      <c r="J43" s="37"/>
+      <c r="K43" s="37"/>
+      <c r="L43" s="37"/>
+      <c r="M43" s="37"/>
+      <c r="N43" s="37"/>
+      <c r="O43" s="38"/>
+      <c r="P43" s="38"/>
+      <c r="Q43" s="38"/>
+      <c r="R43" s="38"/>
+      <c r="S43" s="38"/>
+      <c r="T43" s="38"/>
+      <c r="U43" s="38"/>
+      <c r="V43" s="38"/>
+      <c r="W43" s="38"/>
+    </row>
+    <row r="44" spans="1:23">
+      <c r="A44" s="37"/>
+      <c r="B44" s="37"/>
+      <c r="C44" s="37"/>
+      <c r="D44" s="37"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="37"/>
+      <c r="H44" s="37"/>
+      <c r="I44" s="37"/>
+      <c r="J44" s="37"/>
+      <c r="K44" s="37"/>
+      <c r="L44" s="37"/>
+      <c r="M44" s="37"/>
+      <c r="N44" s="37"/>
+      <c r="O44" s="38"/>
+      <c r="P44" s="38"/>
+      <c r="Q44" s="38"/>
+      <c r="R44" s="38"/>
+      <c r="S44" s="38"/>
+      <c r="T44" s="38"/>
+      <c r="U44" s="38"/>
+      <c r="V44" s="38"/>
+      <c r="W44" s="38"/>
+    </row>
+    <row r="45" spans="1:23" ht="15.5">
+      <c r="A45" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="B45" s="35"/>
-      <c r="C45" s="35"/>
-      <c r="D45" s="35"/>
-      <c r="E45" s="35"/>
-      <c r="F45" s="35"/>
-      <c r="G45" s="35" t="s">
+      <c r="B45" s="37"/>
+      <c r="C45" s="37"/>
+      <c r="D45" s="37"/>
+      <c r="E45" s="37"/>
+      <c r="F45" s="37"/>
+      <c r="G45" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="H45" s="35"/>
-      <c r="I45" s="35"/>
-      <c r="J45" s="35"/>
-      <c r="K45" s="35"/>
-      <c r="L45" s="35"/>
-      <c r="M45" s="35"/>
-      <c r="N45" s="35"/>
-      <c r="O45" s="35" t="s">
+      <c r="H45" s="37"/>
+      <c r="I45" s="37"/>
+      <c r="J45" s="37"/>
+      <c r="K45" s="37"/>
+      <c r="L45" s="37"/>
+      <c r="M45" s="37"/>
+      <c r="N45" s="37"/>
+      <c r="O45" s="37" t="s">
         <v>37</v>
       </c>
-      <c r="P45" s="35"/>
-      <c r="Q45" s="35"/>
-      <c r="R45" s="35"/>
-      <c r="S45" s="35"/>
-      <c r="T45" s="35"/>
-      <c r="U45" s="35"/>
-      <c r="V45" s="35"/>
-      <c r="W45" s="35"/>
-    </row>
-    <row r="46" spans="1:23" ht="33.5">
-      <c r="A46" s="37"/>
-      <c r="B46" s="37"/>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
+      <c r="P45" s="37"/>
+      <c r="Q45" s="37"/>
+      <c r="R45" s="37"/>
+      <c r="S45" s="37"/>
+      <c r="T45" s="37"/>
+      <c r="U45" s="37"/>
+      <c r="V45" s="37"/>
+      <c r="W45" s="37"/>
+    </row>
+    <row r="46" spans="1:23" ht="15.5">
+      <c r="A46" s="39"/>
+      <c r="B46" s="39"/>
+      <c r="C46" s="39"/>
+      <c r="D46" s="39"/>
+      <c r="E46" s="39"/>
+      <c r="F46" s="39"/>
       <c r="G46" s="39"/>
       <c r="H46" s="39"/>
       <c r="I46" s="39"/>
@@ -2387,11 +2333,11 @@
       <c r="R47" s="8"/>
       <c r="S47" s="8"/>
       <c r="T47" s="8"/>
-      <c r="U47" s="36" t="s">
+      <c r="U47" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="V47" s="36"/>
-      <c r="W47" s="36"/>
+      <c r="V47" s="34"/>
+      <c r="W47" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="21">
